--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/ARIZONA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/ARIZONA_2015.xlsx
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C144">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C192">
@@ -5035,7 +5035,7 @@
         <v>13</v>
       </c>
       <c r="D260">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="261">
@@ -5737,7 +5737,7 @@
         <v>13</v>
       </c>
       <c r="D299">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="300">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C314">
@@ -6079,7 +6079,7 @@
         <v>13</v>
       </c>
       <c r="D318">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="319">
@@ -6637,7 +6637,7 @@
         <v>13</v>
       </c>
       <c r="D349">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="350">
@@ -10075,7 +10075,7 @@
         <v>13</v>
       </c>
       <c r="D540">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="541">
@@ -10237,7 +10237,7 @@
         <v>13</v>
       </c>
       <c r="D549">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="550">
@@ -11677,7 +11677,7 @@
         <v>13</v>
       </c>
       <c r="D629">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="630">
@@ -13243,7 +13243,7 @@
         <v>13</v>
       </c>
       <c r="D716">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="717">
@@ -14485,7 +14485,7 @@
         <v>13</v>
       </c>
       <c r="D785">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="786">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C803">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C804">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C830">
@@ -15565,7 +15565,7 @@
         <v>13</v>
       </c>
       <c r="D845">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="846">
@@ -15961,7 +15961,7 @@
         <v>13</v>
       </c>
       <c r="D867">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="868">
@@ -18373,7 +18373,7 @@
         <v>13</v>
       </c>
       <c r="D1001">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="1002">
@@ -18535,7 +18535,7 @@
         <v>13</v>
       </c>
       <c r="D1010">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="1011">
@@ -18931,7 +18931,7 @@
         <v>13</v>
       </c>
       <c r="D1032">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="1033">
@@ -19417,7 +19417,7 @@
         <v>13</v>
       </c>
       <c r="D1059">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="1060">
@@ -20317,7 +20317,7 @@
         <v>13</v>
       </c>
       <c r="D1109">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="1110">
@@ -21138,7 +21138,7 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1155">
@@ -23665,7 +23665,7 @@
         <v>13</v>
       </c>
       <c r="D1295">
-        <v>0.0009418242411070057</v>
+        <v>0.0009418242411070056</v>
       </c>
     </row>
     <row r="1296">
